--- a/excel-003-practice.xlsx
+++ b/excel-003-practice.xlsx
@@ -483,7 +483,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="31"/>
